--- a/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -724,6 +724,94 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01M0HF6ECXQQ67GF7762Y9X1R6</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0HF6ECXQQ67GF7762Y9X1R6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ITSM Configuration</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01M0HFN4XDMNCZ13QE72T78RKY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0HFN4XDMNCZ13QE72T78RKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Messaging Applications</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01M0HFQBW6TTCX4BBPSE8TESE7</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0HFQBW6TTCX4BBPSE8TESE7</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JML Ticket Creation</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>h_01M0HFSDMMYB6CYWV3CD5G6Z7A</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0HFSDMMYB6CYWV3CD5G6Z7A</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -812,6 +812,94 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ticket Creation Configuration</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01M0HR0XKB3B8XEN8RQNA147E9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0HR0XKB3B8XEN8RQNA147E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01M0J6QE2AA1AAADRYBSQYVZ02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0J6QE2AA1AAADRYBSQYVZ02</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01M0J707HQT96YCSHWJ38K6JYT</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0J707HQT96YCSHWJ38K6JYT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Define Notification Channel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01M0J710WGAQ2XM5ZYMD1NEP3T</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0J710WGAQ2XM5ZYMD1NEP3T</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,6 +900,28 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Notification Configuration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01M0S1WC30VCECNMS6XX33YGJ2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S1WC30VCECNMS6XX33YGJ2</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
+++ b/site/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -922,6 +922,226 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01M0S608QR2KME2NSZDF1D17FT</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S608QR2KME2NSZDF1D17FT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Logging Settings</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01M0S66YD5MJFXEP8E7G5NR5P1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S66YD5MJFXEP8E7G5NR5P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Report Settings</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01M0S675SS16AYCAQFPH1GVBV3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S675SS16AYCAQFPH1GVBV3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Log Insights Settings</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01M0S67CSY20G6G00FDGKDVGDE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S67CSY20G6G00FDGKDVGDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01M0S6E7HPTZ7FPMC4RJDE1GJC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S6E7HPTZ7FPMC4RJDE1GJC</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Advanced Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01M0S6EYC4DWBACK0MRVFRST0E</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01M0S6EYC4DWBACK0MRVFRST0E</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01KVWRPTWRN33APTZ4EAFVBT22</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-ITSM-SolarWinds-Service-Desk-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
